--- a/branches/chore/update-miabis-1.3.0/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
+++ b/branches/chore/update-miabis-1.3.0/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:37:22+00:00</t>
+    <t>2026-09-10T10:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/update-miabis-1.3.0/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
+++ b/branches/chore/update-miabis-1.3.0/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:48:22+00:00</t>
+    <t>2026-09-10T11:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/update-miabis-1.3.0/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
+++ b/branches/chore/update-miabis-1.3.0/StructureDefinition-mii-ex-biobank-anzahl-passagen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:13:05+00:00</t>
+    <t>2026-09-10T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
